--- a/output/final/dc/dc distributors (status checked)/status_check_report.xlsx
+++ b/output/final/dc/dc distributors (status checked)/status_check_report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status changes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$108</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Status changes'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1843,121 +1843,121 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
+          <t>Drive Control Corporation Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>drivecon.net</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Kleoss Capital</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Acquired by Kleoss Capital and private investors in October 2023 and rebranded DCC Technologies; still trading (ITWeb).</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>AT Computers a.s.</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>atcomp.cz</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>AB Group</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>AT Computers is active as a leading ICT distributor and is part of the Polish AB Group following an acquisition in October 2007.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>renamed</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Accu-Tech LLC</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>accu-tech.com</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Anixter</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Accu-Tech was acquired by Anixter on January 1, 1997, according to PitchBook.</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>renamed</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Prianto UK</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>prianto.com</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>QBS Software</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>Prianto joined QBS Technology Group in early 2025 and has since merged into QBS Software GmbH, according to the official company website.</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>removed</t>
         </is>
       </c>
     </row>
@@ -1969,37 +1969,37 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mayflex Group Ltd</t>
+          <t>Prianto UK</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>mayflex.com</t>
+          <t>prianto.com</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sonepar UK</t>
+          <t>QBS Software</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>According to PitchBook data, Mayflex was acquired by Sonepar UK in 2015 but continues to operate under its own brand.</t>
+          <t>Prianto joined QBS Technology Group in early 2025 and has since merged into QBS Software GmbH, according to the official company website.</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>ICOS (acquired by Computer Gross Italia S.p.A.)</t>
+          <t>Mayflex Group Ltd</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>icosvad.com</t>
+          <t>mayflex.com</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Computer Gross Italia S.p.A.</t>
+          <t>Sonepar UK</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Computer Gross Italia S.p.A. completed the acquisition of a 51% majority stake in ICOS S.p.A. in November 2017 (Sesa S.p.A. press release).</t>
+          <t>According to PitchBook data, Mayflex was acquired by Sonepar UK in 2015 but continues to operate under its own brand.</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -2053,117 +2053,121 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
+          <t>ICOS (acquired by Computer Gross Italia S.p.A.)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>icosvad.com</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Computer Gross Italia S.p.A.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Computer Gross Italia S.p.A. completed the acquisition of a 51% majority stake in ICOS S.p.A. in November 2017 (Sesa S.p.A. press release).</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="33" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
           <t>NWS</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>nwsnext.com</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Grain Management</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Network Wireless Solutions (NWS) is a portfolio company that was acquired by investment firm Grain Management in 2021, according to official reports on nwsnext.com.</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>renamed</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>DCC A/S (acquired by Foxway)</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>dcc.dk</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>absorbed</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Foxway</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>According to the Foxway history page, Foxway acquired DCC A/S in 2021.</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="33" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>TMC Technology</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>tmc-uk.com</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>IBASE Technology Inc.</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>TMC Technology operates as IBASE Europe, which is a wholly-owned subsidiary of IBASE Technology Inc. according to official product catalogs and partnership directories.</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2179,12 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Ingram Micro Holding Corporation</t>
+          <t>TMC Technology</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>https://www.ingrammicro.com</t>
+          <t>tmc-uk.com</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2190,17 +2194,13 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Platinum Equity, LLC</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>IBASE Technology Inc.</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Ingram Micro Holding Corporation was acquired by affiliates of Platinum Equity, LLC on July 2, 2021, per a company prospectus filing with the SEC.</t>
+          <t>TMC Technology operates as IBASE Europe, which is a wholly-owned subsidiary of IBASE Technology Inc. according to official product catalogs and partnership directories.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -2217,112 +2217,112 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
+          <t>Ingram Micro Holding Corporation</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ingrammicro.com</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Platinum Equity, LLC</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Ingram Micro Holding Corporation was acquired by affiliates of Platinum Equity, LLC on July 2, 2021, per a company prospectus filing with the SEC.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="33" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
           <t>Anixter (Wesco subsidiary) (acquired by Wesco)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>anixter.com</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Wesco International</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Wesco International completed its acquisition of Anixter International on June 22, 2020, according to an official Wesco press release.</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>renamed</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Action Europe</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>action.eu</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Action Europe GmbH entered liquidation and ceased trading in September 2020, as reported by Dutch IT Channel.</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="33" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Almo Corporation (acquired by Exertis)</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>almo.com</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>absorbed</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Exertis</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Almo Corporation was acquired by DCC Technology (Exertis) in December 2021 and subsequently rebranded its Pro AV operations as Exertis Almo.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Veracomp - Ingram Micro SA (acquired by Exclusive Networks)</t>
+          <t>Almo Corporation (acquired by Exertis)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>veracomp.pl</t>
+          <t>almo.com</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Exclusive Networks</t>
+          <t>Exertis</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Exclusive Networks completed the acquisition of Veracomp SA on December 30, 2020.</t>
+          <t>Almo Corporation was acquired by DCC Technology (Exertis) in December 2021 and subsequently rebranded its Pro AV operations as Exertis Almo.</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Tech Data Advanced Solutions (UK) Ltd (acquired by TD SYNNEX)</t>
+          <t>Veracomp - Ingram Micro SA (acquired by Exclusive Networks)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>tdsynnex.com</t>
+          <t>veracomp.pl</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>TD SYNNEX Corporation</t>
+          <t>Exclusive Networks</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tech Data Corporation, the owner of Tech Data Advanced Solutions (UK), was acquired by SYNNEX Corporation in 2021 to form TD SYNNEX, which completely absorbed its operations.</t>
+          <t>Exclusive Networks completed the acquisition of Veracomp SA on December 30, 2020.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Sager Electronics (acquired by TTI, Inc.)</t>
+          <t>Tech Data Advanced Solutions (UK) Ltd (acquired by TD SYNNEX)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>https://www.sager.com</t>
+          <t>tdsynnex.com</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>absorbed</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>TTI, Inc.</t>
+          <t>TD SYNNEX Corporation</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Sager Electronics was acquired by TTI, Inc. in 2012 and operates as a wholly owned subsidiary according to PitchBook and Reuters.</t>
+          <t>Tech Data Corporation, the owner of Tech Data Advanced Solutions (UK), was acquired by SYNNEX Corporation in 2021 to form TD SYNNEX, which completely absorbed its operations.</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>renamed</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2465,37 +2465,37 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Ryosan Company (acquired by Ryoyo Ryosan, Inc.)</t>
+          <t>Sager Electronics (acquired by TTI, Inc.)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>ryosan.co.jp</t>
+          <t>https://www.sager.com</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>absorbed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Ryoyo Ryosan Holdings, Inc.</t>
+          <t>TTI, Inc.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Ryosan Company was merged with Ryoyo Electro into the combined operating entity Ryoyo Ryosan, Inc. effective April 1, 2026, according to TipRanks.</t>
+          <t>Sager Electronics was acquired by TTI, Inc. in 2012 and operates as a wholly owned subsidiary according to PitchBook and Reuters.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>renamed</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>PNH Technology (acquired by Sourcing Solutions LLC)</t>
+          <t>Ryosan Company (acquired by Ryoyo Ryosan, Inc.)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>pnhtech.com</t>
+          <t>ryosan.co.jp</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Sourcing Solutions LLC</t>
+          <t>Ryoyo Ryosan Holdings, Inc.</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PNH Technology and Sourcing Solutions LLC entered into a definitive merger agreement in November 2018 according to a press release on PRLog.</t>
+          <t>Ryosan Company was merged with Ryoyo Electro into the combined operating entity Ryoyo Ryosan, Inc. effective April 1, 2026, according to TipRanks.</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -2549,71 +2549,79 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
+          <t>PNH Technology (acquired by Sourcing Solutions LLC)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>pnhtech.com</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>absorbed</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sourcing Solutions LLC</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>PNH Technology and Sourcing Solutions LLC entered into a definitive merger agreement in November 2018 according to a press release on PRLog.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="33" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>Tech Data (CDW/TD SYNNEX)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>tdsynnex.com</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>absorbed</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>SYNNEX Corporation</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Tech Data merged with SYNNEX Corporation on September 1, 2021, to create the combined entity TD SYNNEX, according to an announcement on the official TD SYNNEX newsroom.</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>dc_distributor_verified_distributors</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Arrow Enterprise Computing Solutions</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>arrow.com</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="9" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Same company as 'Arrow Electronics' (same website and country, or same name and city) - listed once.</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>duplicate</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2633,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Arrow Electronics, Inc.</t>
+          <t>Arrow Enterprise Computing Solutions</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2659,12 +2667,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Redington MEA</t>
+          <t>Arrow Electronics, Inc.</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>https://redingtongroup.com</t>
+          <t>arrow.com</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2676,7 +2684,7 @@
       <c r="F53" s="9" t="inlineStr"/>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Redington Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Arrow Electronics' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -2693,12 +2701,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Exclusive Networks SA</t>
+          <t>Redington MEA</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>exclusive-networks.com</t>
+          <t>https://redingtongroup.com</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2710,7 +2718,7 @@
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Exclusive Networks' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Redington Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2727,12 +2735,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Esprinet SpA</t>
+          <t>Exclusive Networks SA</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>esprinet.com</t>
+          <t>exclusive-networks.com</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2744,7 +2752,7 @@
       <c r="F55" s="9" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Esprinet S.p.A.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Exclusive Networks' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -2761,12 +2769,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Macnica, Inc.</t>
+          <t>Esprinet SpA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>www.macnica.co.jp</t>
+          <t>esprinet.com</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2778,7 +2786,7 @@
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Macnica Holdings' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Esprinet S.p.A.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -2795,12 +2803,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>WPG Holdings Limited</t>
+          <t>Macnica, Inc.</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>wpgholdings.com</t>
+          <t>www.macnica.co.jp</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2812,7 +2820,7 @@
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'WPG Holdings' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Macnica Holdings' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -2821,7 +2829,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="33" customHeight="1">
+    <row r="58" ht="24" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -2829,12 +2837,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Ingram Micro Inc. (acquired by Platinum Equity)</t>
+          <t>WPG Holdings Limited</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>ingrammicro.com</t>
+          <t>wpgholdings.com</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2846,7 +2854,7 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Ingram Micro Holding Corporation (acquired by Platinum Equity, LLC)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'WPG Holdings' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -2855,7 +2863,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
+    <row r="59" ht="33" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -2863,12 +2871,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>D&amp;H Distributing</t>
+          <t>Ingram Micro Inc. (acquired by Platinum Equity)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>dandh.com</t>
+          <t>ingrammicro.com</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2880,7 +2888,7 @@
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'D&amp;H Distributing Co.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Ingram Micro Holding Corporation (acquired by Platinum Equity, LLC)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -2897,12 +2905,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>VSTECS Holdings Limited</t>
+          <t>D&amp;H Distributing</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vstecs.com</t>
+          <t>dandh.com</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2914,7 +2922,7 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'VST ECS Holdings Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'D&amp;H Distributing Co.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -2931,7 +2939,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>VST ECS</t>
+          <t>VSTECS Holdings Limited</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -2965,12 +2973,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Infinigate Holding GmbH</t>
+          <t>VST ECS</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>infinigate.com</t>
+          <t>vstecs.com</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2982,7 +2990,7 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Infinigate Group' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'VST ECS Holdings Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -2999,12 +3007,12 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Dicker Data Limited</t>
+          <t>Infinigate Holding GmbH</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>dickerdata.com.au</t>
+          <t>infinigate.com</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -3016,7 +3024,7 @@
       <c r="F63" s="9" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Dicker Data' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Infinigate Group' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -3025,7 +3033,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="33" customHeight="1">
+    <row r="64" ht="24" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3033,12 +3041,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>ADN Distribution GmbH</t>
+          <t>Dicker Data Limited</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>adn.de</t>
+          <t>dickerdata.com.au</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3050,7 +3058,7 @@
       <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'ADN Advanced Digital Network Distribution GmbH' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Dicker Data' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3067,12 +3075,12 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Savex Technologies</t>
+          <t>ADN Distribution GmbH</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>savex.in</t>
+          <t>adn.de</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -3084,7 +3092,7 @@
       <c r="F65" s="9" t="inlineStr"/>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Savex Technologies Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'ADN Advanced Digital Network Distribution GmbH' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -3101,12 +3109,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Intcomex</t>
+          <t>Savex Technologies</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>intcomex.com</t>
+          <t>savex.in</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3118,7 +3126,7 @@
       <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Intcomex, Inc. (acquired by Citigroup Venture Capital International)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Savex Technologies Pvt. Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -3127,7 +3135,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
+    <row r="67" ht="33" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3135,12 +3143,12 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Mindware FZCO</t>
+          <t>Intcomex</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>mindware.net</t>
+          <t>intcomex.com</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3152,7 +3160,7 @@
       <c r="F67" s="9" t="inlineStr"/>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Mindware FZ LLC' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Intcomex, Inc. (acquired by Citigroup Venture Capital International)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -3161,7 +3169,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="33" customHeight="1">
+    <row r="68" ht="24" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3169,12 +3177,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Logicom Public Ltd</t>
+          <t>Mindware FZCO</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>logicomdistribution.net</t>
+          <t>mindware.net</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3186,7 +3194,7 @@
       <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Logicom Public Company Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Mindware FZ LLC' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3203,7 +3211,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Logicom Distribution</t>
+          <t>Logicom Public Ltd</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -3229,7 +3237,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
+    <row r="70" ht="33" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3237,12 +3245,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Elko Group</t>
+          <t>Logicom Distribution</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>elkogroup.com</t>
+          <t>logicomdistribution.net</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3254,7 +3262,7 @@
       <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'ELKO Grupa AS' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Logicom Public Company Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -3263,7 +3271,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="33" customHeight="1">
+    <row r="71" ht="24" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3271,12 +3279,12 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Pinnacle Micro (Pty) Ltd</t>
+          <t>Elko Group</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>pinnacle.co.za</t>
+          <t>elkogroup.com</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3288,7 +3296,7 @@
       <c r="F71" s="9" t="inlineStr"/>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Pinnacle ICT (acquired by Alviva Holdings)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'ELKO Grupa AS' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -3297,7 +3305,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
+    <row r="72" ht="33" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3305,12 +3313,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CMS Distribution</t>
+          <t>Pinnacle Micro (Pty) Ltd</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>cmsdistribution.com</t>
+          <t>pinnacle.co.za</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3322,7 +3330,7 @@
       <c r="F72" s="5" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'CMS Distribution Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Pinnacle ICT (acquired by Alviva Holdings)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -3339,12 +3347,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Siewert e Kau</t>
+          <t>CMS Distribution</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>siewert-kau.de</t>
+          <t>cmsdistribution.com</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3356,7 +3364,7 @@
       <c r="F73" s="9" t="inlineStr"/>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Siewert &amp; Kau' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'CMS Distribution Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -3373,12 +3381,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Northamber</t>
+          <t>Siewert e Kau</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>northamber.com</t>
+          <t>siewert-kau.de</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3390,7 +3398,7 @@
       <c r="F74" s="5" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Northamber PLC' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Siewert &amp; Kau' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -3407,12 +3415,12 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Bluechip Infotech Pty Ltd</t>
+          <t>Northamber</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>bluechipit.com.au</t>
+          <t>northamber.com</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3424,7 +3432,7 @@
       <c r="F75" s="9" t="inlineStr"/>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Bluechip Infotech' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Northamber PLC' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
@@ -3441,12 +3449,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Rectron (Pty) Ltd (acquired by Mustek Limited)</t>
+          <t>iValue InfoSolutions</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>rectron.co.za</t>
+          <t>ivalue.co.in</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3458,7 +3466,7 @@
       <c r="F76" s="5" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Rectron (acquired by Mustek Limited)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'iValue InfoSolutions Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -3475,12 +3483,12 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Pedab Group AB</t>
+          <t>Bluechip Infotech Pty Ltd</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>pedab.com</t>
+          <t>bluechipit.com.au</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -3492,7 +3500,7 @@
       <c r="F77" s="9" t="inlineStr"/>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Pedab' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Bluechip Infotech' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
@@ -3509,12 +3517,12 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Supertron Electronics Pvt. Ltd.</t>
+          <t>Rectron (Pty) Ltd (acquired by Mustek Limited)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>supertronindia.com</t>
+          <t>rectron.co.za</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3526,7 +3534,7 @@
       <c r="F78" s="5" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Supertron Electronics Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Rectron (acquired by Mustek Limited)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -3535,7 +3543,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="33" customHeight="1">
+    <row r="79" ht="24" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3543,12 +3551,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Supertron Electronics</t>
+          <t>Pedab Group AB</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>supertronindia.com</t>
+          <t>pedab.com</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -3560,7 +3568,7 @@
       <c r="F79" s="9" t="inlineStr"/>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Supertron Electronics Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Pedab' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -3577,12 +3585,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Titan Data Solutions</t>
+          <t>Supertron Electronics Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>titandatasolutions.com</t>
+          <t>supertronindia.com</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3594,7 +3602,7 @@
       <c r="F80" s="5" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Titan Data Solutions Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Supertron Electronics Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -3603,7 +3611,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1">
+    <row r="81" ht="33" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3611,12 +3619,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Stovaris</t>
+          <t>Supertron Electronics</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>stovaris.pl</t>
+          <t>supertronindia.com</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -3628,7 +3636,7 @@
       <c r="F81" s="9" t="inlineStr"/>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Stovaris Sp. z o.o.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Supertron Electronics Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -3645,12 +3653,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Distology Ltd (acquired by Foresight Group)</t>
+          <t>Titan Data Solutions</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>distology.com</t>
+          <t>titandatasolutions.com</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3662,7 +3670,7 @@
       <c r="F82" s="5" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Distology Limited (acquired by Foresight Group)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Titan Data Solutions Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -3679,12 +3687,12 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>EPS Global</t>
+          <t>Stovaris</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>epsglobal.com</t>
+          <t>stovaris.pl</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -3696,7 +3704,7 @@
       <c r="F83" s="9" t="inlineStr"/>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'EPS Global Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Stovaris Sp. z o.o.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
@@ -3705,7 +3713,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
+    <row r="84" ht="33" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3713,12 +3721,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Copaco</t>
+          <t>Distology Ltd (acquired by Foresight Group)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>copaco.com</t>
+          <t>distology.com</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3730,7 +3738,7 @@
       <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Copaco N.V.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Distology Limited (acquired by Foresight Group)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -3739,7 +3747,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="33" customHeight="1">
+    <row r="85" ht="24" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3747,12 +3755,12 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>ICOS (acquired by Computer Gross Italia S.p.A.)</t>
+          <t>EPS Global</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>icosvad.com</t>
+          <t>epsglobal.com</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -3764,7 +3772,7 @@
       <c r="F85" s="9" t="inlineStr"/>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'ICOS S.p.A. (acquired by Computer Gross Italia S.p.A.)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'EPS Global Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
@@ -3773,7 +3781,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="33" customHeight="1">
+    <row r="86" ht="24" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3781,12 +3789,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>CLM Controller Latinoamerica S.A.</t>
+          <t>Copaco</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>clm.tech</t>
+          <t>copaco.com</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3798,7 +3806,7 @@
       <c r="F86" s="5" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'CLM Technology &amp; Relationship' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Copaco N.V.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -3815,12 +3823,12 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>CLM Tech</t>
+          <t>ICOS (acquired by Computer Gross Italia S.p.A.)</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>clm.tech</t>
+          <t>icosvad.com</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -3832,7 +3840,7 @@
       <c r="F87" s="9" t="inlineStr"/>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'CLM Technology &amp; Relationship' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'ICOS S.p.A. (acquired by Computer Gross Italia S.p.A.)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
@@ -3849,12 +3857,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Gulf Applications</t>
+          <t>CLM Controller Latinoamerica S.A.</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>https://www.gapp.sa</t>
+          <t>clm.tech</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3866,7 +3874,7 @@
       <c r="F88" s="5" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Gulf Applications Co. (GAPP)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'CLM Technology &amp; Relationship' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -3875,7 +3883,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="24" customHeight="1">
+    <row r="89" ht="33" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3883,12 +3891,12 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Ampconnect</t>
+          <t>CLM Tech</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>ampconnectme.com</t>
+          <t>clm.tech</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -3900,7 +3908,7 @@
       <c r="F89" s="9" t="inlineStr"/>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'AMP Connect ME' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'CLM Technology &amp; Relationship' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
@@ -3917,12 +3925,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>TechnoBind</t>
+          <t>Gulf Applications</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>technobind.com</t>
+          <t>https://www.gapp.sa</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -3934,7 +3942,7 @@
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'TechnoBind Solutions Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Gulf Applications Co. (GAPP)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -3943,7 +3951,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="33" customHeight="1">
+    <row r="91" ht="24" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3951,12 +3959,12 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>TechnoBind Solutions Pvt. Ltd.</t>
+          <t>Ampconnect</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>technobind.com</t>
+          <t>ampconnectme.com</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -3968,7 +3976,7 @@
       <c r="F91" s="9" t="inlineStr"/>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'TechnoBind Solutions Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'AMP Connect ME' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
@@ -3977,7 +3985,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
+    <row r="92" ht="33" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -3985,12 +3993,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>RAH Infotech Pvt. Ltd.</t>
+          <t>TechnoBind</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>rahinfotech.com</t>
+          <t>technobind.com</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4002,7 +4010,7 @@
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'RAH Infotech Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'TechnoBind Solutions Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -4011,7 +4019,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="24" customHeight="1">
+    <row r="93" ht="33" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -4019,12 +4027,12 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>RAH Infotech</t>
+          <t>TechnoBind Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>rahinfotech.com</t>
+          <t>technobind.com</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4036,7 +4044,7 @@
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'RAH Infotech Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'TechnoBind Solutions Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
@@ -4053,12 +4061,12 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Sariya IT</t>
+          <t>RAH Infotech Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>sariya-it.com</t>
+          <t>rahinfotech.com</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4070,7 +4078,7 @@
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Sariya IT Distribution' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'RAH Infotech Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -4087,12 +4095,12 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Heilind Electronics, Inc.</t>
+          <t>RAH Infotech</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>heilind.com</t>
+          <t>rahinfotech.com</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4104,7 +4112,7 @@
       <c r="F95" s="9" t="inlineStr"/>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Heilind Electronics' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'RAH Infotech Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
@@ -4121,12 +4129,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Arbitech LLC</t>
+          <t>Sariya IT</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>arbitech.com</t>
+          <t>sariya-it.com</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4138,7 +4146,7 @@
       <c r="F96" s="5" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Arbitech, LLC' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Sariya IT Distribution' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -4155,12 +4163,12 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>ASBIS Enterprises PLC</t>
+          <t>Heilind Electronics, Inc.</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>asbis.com</t>
+          <t>heilind.com</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
@@ -4172,7 +4180,7 @@
       <c r="F97" s="9" t="inlineStr"/>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'ASBIS' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Heilind Electronics' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
@@ -4181,7 +4189,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="24" customHeight="1">
+    <row r="98" ht="33" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -4189,12 +4197,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Iris Global Services Pvt. Ltd.</t>
+          <t>Drive Control Corporation Pty Ltd (acquired by Kleoss Capital)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>irisglobal.in</t>
+          <t>drivecon.net</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4206,7 +4214,7 @@
       <c r="F98" s="5" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Iris Global Services' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Drive Control Corporation (Pty) Ltd (acquired by Kleoss Capital)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -4223,12 +4231,12 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>eNOVA Technologies</t>
+          <t>Arbitech LLC</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>https://enova.sg</t>
+          <t>arbitech.com</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -4240,7 +4248,7 @@
       <c r="F99" s="9" t="inlineStr"/>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'eNOVA Technologies Pte Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Arbitech, LLC' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
@@ -4257,12 +4265,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Graybar</t>
+          <t>Ethos Technology Ltd.</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>graybar.com</t>
+          <t>ethostechnology.co.uk</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4274,7 +4282,7 @@
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Graybar Electric Company' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Ethos Technology Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -4291,12 +4299,12 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Wesco Distribution</t>
+          <t>ASBIS Enterprises PLC</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>wesco.com</t>
+          <t>asbis.com</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -4308,7 +4316,7 @@
       <c r="F101" s="9" t="inlineStr"/>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'WESCO International' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'ASBIS' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
@@ -4317,7 +4325,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="33" customHeight="1">
+    <row r="102" ht="24" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>dc_distributor_verified_distributors</t>
@@ -4325,12 +4333,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Computer Infotech (India) Pvt. Ltd.</t>
+          <t>Iris Global Services Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>cominfo.in</t>
+          <t>irisglobal.in</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4342,7 +4350,7 @@
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Computer Infotech (India) Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Iris Global Services' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -4359,12 +4367,12 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Distecna S.A.</t>
+          <t>eNOVA Technologies</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>https://www.distecna.com</t>
+          <t>https://enova.sg</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -4376,7 +4384,7 @@
       <c r="F103" s="9" t="inlineStr"/>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Distecna' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'eNOVA Technologies Pte Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
@@ -4393,12 +4401,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>MegaCore Supplies doo</t>
+          <t>Graybar</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>megacore.rs</t>
+          <t>graybar.com</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -4410,17 +4418,153 @@
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
+          <t>Same company as 'Graybar Electric Company' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Wesco Distribution</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>wesco.com</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'WESCO International' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="33" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Computer Infotech (India) Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>cominfo.in</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Computer Infotech (India) Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Distecna S.A.</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>https://www.distecna.com</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Distecna' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>dc_distributor_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>MegaCore Supplies doo</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>megacore.rs</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
           <t>Same company as 'MegaCore Supplies' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
-      <c r="H104" s="5" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>duplicate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H104"/>
+  <autoFilter ref="A1:H108"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -4525,6 +4669,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
